--- a/data/trans_bre/IP1019-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1019-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,0</t>
+          <t>-3,48; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,34</t>
+          <t>-0,2; 0,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
